--- a/Bike_Sales_Outlier_Lab.xlsx
+++ b/Bike_Sales_Outlier_Lab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dropbox\Dropbox\Cisco Aries\2022\Data Pathway Course Development\Course 1\Rework\csv files for reworked labs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\OneDrive\Desktop\STATS ASSIGNMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00FEFAE0-DE00-419C-BA87-533F9603AF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA69AA4C-C6DC-4694-BC05-A295D5AE6855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bike Sales" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="161">
   <si>
     <t>Sales_Order #</t>
   </si>
@@ -501,6 +499,21 @@
   </si>
   <si>
     <t>000261782</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>STD DEV</t>
+  </si>
+  <si>
+    <t>CV</t>
   </si>
 </sst>
 </file>
@@ -508,7 +521,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1009,7 +1022,7 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1377,25 +1390,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S94"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
@@ -1515,7 +1528,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -1576,7 +1589,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1637,7 +1650,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -1698,7 +1711,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -1759,7 +1772,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -1820,7 +1833,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1881,7 +1894,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -1942,7 +1955,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>47</v>
       </c>
@@ -2003,7 +2016,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
@@ -2064,7 +2077,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>51</v>
       </c>
@@ -2125,7 +2138,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>54</v>
       </c>
@@ -2186,7 +2199,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -2247,7 +2260,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
@@ -2308,7 +2321,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>59</v>
       </c>
@@ -2369,7 +2382,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>61</v>
       </c>
@@ -2430,7 +2443,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
@@ -2491,7 +2504,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -2552,7 +2565,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>65</v>
       </c>
@@ -2613,7 +2626,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2674,7 +2687,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
@@ -2735,7 +2748,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>71</v>
       </c>
@@ -2796,7 +2809,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>72</v>
       </c>
@@ -2857,7 +2870,7 @@
         <v>6750</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>75</v>
       </c>
@@ -2918,7 +2931,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>77</v>
       </c>
@@ -2979,7 +2992,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>78</v>
       </c>
@@ -3040,7 +3053,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>79</v>
       </c>
@@ -3101,7 +3114,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>80</v>
       </c>
@@ -3162,7 +3175,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
@@ -3223,7 +3236,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>84</v>
       </c>
@@ -3284,7 +3297,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>85</v>
       </c>
@@ -3345,7 +3358,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
@@ -3406,7 +3419,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>89</v>
       </c>
@@ -3467,7 +3480,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>90</v>
       </c>
@@ -3528,7 +3541,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>91</v>
       </c>
@@ -3589,7 +3602,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>92</v>
       </c>
@@ -3650,7 +3663,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>93</v>
       </c>
@@ -3711,7 +3724,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>94</v>
       </c>
@@ -3772,7 +3785,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>95</v>
       </c>
@@ -3833,7 +3846,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>96</v>
       </c>
@@ -3894,7 +3907,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>97</v>
       </c>
@@ -3955,7 +3968,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>98</v>
       </c>
@@ -4016,7 +4029,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>100</v>
       </c>
@@ -4077,7 +4090,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>101</v>
       </c>
@@ -4138,7 +4151,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>102</v>
       </c>
@@ -4199,7 +4212,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>103</v>
       </c>
@@ -4260,7 +4273,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>104</v>
       </c>
@@ -4321,7 +4334,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>105</v>
       </c>
@@ -4382,7 +4395,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>106</v>
       </c>
@@ -4443,7 +4456,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>107</v>
       </c>
@@ -4504,7 +4517,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>108</v>
       </c>
@@ -4565,7 +4578,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>111</v>
       </c>
@@ -4626,7 +4639,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>112</v>
       </c>
@@ -4687,7 +4700,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>113</v>
       </c>
@@ -4748,7 +4761,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>114</v>
       </c>
@@ -4809,7 +4822,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>115</v>
       </c>
@@ -4870,7 +4883,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>116</v>
       </c>
@@ -4931,7 +4944,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>118</v>
       </c>
@@ -4992,7 +5005,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>119</v>
       </c>
@@ -5053,7 +5066,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -5114,7 +5127,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>121</v>
       </c>
@@ -5175,7 +5188,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>122</v>
       </c>
@@ -5236,7 +5249,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>124</v>
       </c>
@@ -5297,7 +5310,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>126</v>
       </c>
@@ -5358,7 +5371,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>127</v>
       </c>
@@ -5419,7 +5432,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>129</v>
       </c>
@@ -5480,7 +5493,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>130</v>
       </c>
@@ -5541,7 +5554,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>131</v>
       </c>
@@ -5602,7 +5615,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>132</v>
       </c>
@@ -5663,7 +5676,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>134</v>
       </c>
@@ -5724,7 +5737,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>136</v>
       </c>
@@ -5785,7 +5798,7 @@
         <v>25520</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>137</v>
       </c>
@@ -5846,7 +5859,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>138</v>
       </c>
@@ -5907,7 +5920,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>139</v>
       </c>
@@ -5968,7 +5981,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>141</v>
       </c>
@@ -6029,7 +6042,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>142</v>
       </c>
@@ -6090,7 +6103,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>143</v>
       </c>
@@ -6151,7 +6164,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>145</v>
       </c>
@@ -6212,7 +6225,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>146</v>
       </c>
@@ -6273,7 +6286,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>147</v>
       </c>
@@ -6334,7 +6347,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>148</v>
       </c>
@@ -6395,7 +6408,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>149</v>
       </c>
@@ -6456,7 +6469,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>150</v>
       </c>
@@ -6517,7 +6530,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>151</v>
       </c>
@@ -6578,7 +6591,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>152</v>
       </c>
@@ -6639,7 +6652,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>153</v>
       </c>
@@ -6700,7 +6713,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>154</v>
       </c>
@@ -6761,7 +6774,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>155</v>
       </c>
@@ -6820,6 +6833,79 @@
       <c r="S89" s="2">
         <f t="shared" si="3"/>
         <v>9180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N90" t="s">
+        <v>156</v>
+      </c>
+      <c r="O90" s="2">
+        <f>AVERAGE(O2:O89)</f>
+        <v>1064.2045454545455</v>
+      </c>
+      <c r="P90" s="2">
+        <f>AVERAGE(P2:P89)</f>
+        <v>1945.659090909091</v>
+      </c>
+      <c r="Q90" s="2">
+        <f>AVERAGE(Q2:Q89)</f>
+        <v>1858.0454545454545</v>
+      </c>
+      <c r="R90" s="2">
+        <f>AVERAGE(R2:R9)</f>
+        <v>1777.75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N91" t="s">
+        <v>157</v>
+      </c>
+      <c r="O91" s="2">
+        <f>MEDIAN(O2:O89)</f>
+        <v>1252</v>
+      </c>
+      <c r="P91" s="2">
+        <f>MEDIAN(P2:P89)</f>
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N92" t="s">
+        <v>158</v>
+      </c>
+      <c r="O92">
+        <f>_xlfn.MODE.SNGL(O2:O89)</f>
+        <v>1252</v>
+      </c>
+      <c r="P92">
+        <f>_xlfn.MODE.SNGL(P2:P89)</f>
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N93" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q93">
+        <f>_xlfn.STDEV.S(Q2:Q89)</f>
+        <v>1399.6977088182489</v>
+      </c>
+      <c r="R93">
+        <f>_xlfn.STDEV.S(R2:R89)</f>
+        <v>2117.3770844770042</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N94" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q94">
+        <f>(_xlfn.STDEV.S(Q2:Q89)/AVERAGE(Q2:Q89))*100</f>
+        <v>75.331725894761064</v>
+      </c>
+      <c r="R94">
+        <f>(_xlfn.STDEV.S(R2:R89)/AVERAGE(R2:R89))*100</f>
+        <v>88.566232904582293</v>
       </c>
     </row>
   </sheetData>
@@ -7066,15 +7152,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="6cf0ffbd-cd96-4ba4-bd4f-bd34e8409846">
@@ -7093,14 +7170,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A449075-01A6-451D-9F66-A0FA0F4FD7AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A449075-01A6-451D-9F66-A0FA0F4FD7AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6cf0ffbd-cd96-4ba4-bd4f-bd34e8409846"/>
+    <ds:schemaRef ds:uri="ef7ae401-bd17-41a5-97cb-ef653218410e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B93B57-25C3-448B-BDF9-E62880BE52EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07A2BFF5-7901-4AE1-9EAC-C53400A8AC57}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6cf0ffbd-cd96-4ba4-bd4f-bd34e8409846"/>
+    <ds:schemaRef ds:uri="ef7ae401-bd17-41a5-97cb-ef653218410e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07A2BFF5-7901-4AE1-9EAC-C53400A8AC57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B93B57-25C3-448B-BDF9-E62880BE52EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>